--- a/financial_advisor_forms/031_travel_expenses_form--financial_advisor_forms.xlsx
+++ b/financial_advisor_forms/031_travel_expenses_form--financial_advisor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>form_id_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>Form Id 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>submitted_at</t>
+          <t>submitted_at_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Submitted At</t>
+          <t>Submitted At 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>submitted_user</t>
+          <t>submitted_user_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Submitted User</t>
+          <t>Submitted User 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>travel_class</t>
+          <t>travel_class_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Travel Class</t>
+          <t>Travel Class 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>submitted_user</t>
+          <t>submitted_user_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Submitted User</t>
+          <t>Submitted User 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'car'}</t>
+          <t>car</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Car'}</t>
+          <t>Car</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'airplane'}</t>
+          <t>airplane</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Airplane'}</t>
+          <t>Airplane</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'bus'}</t>
+          <t>bus</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Bus'}</t>
+          <t>Bus</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'hr'}</t>
+          <t>hr</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'HR'}</t>
+          <t>HR</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'accounting'}</t>
+          <t>accounting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Accounting'}</t>
+          <t>Accounting</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'chatjimmy',_'value':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'chatjimmy', 'value': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'chatjimmy',_'value':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'chatjimmy', 'value': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'business'}</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Business'}</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'personal'}</t>
+          <t>personal</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Personal'}</t>
+          <t>Personal</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'company'}</t>
+          <t>company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Company'}</t>
+          <t>Company</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'chatjimmy',_'value':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'chatjimmy', 'value': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1369,131 +1369,131 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>submitted_user_choices</t>
+          <t>submitted_user_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'chatjimmy',_'value':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'chatjimmy', 'value': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>submitted_user_choices</t>
+          <t>submitted_user_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>travel_class_choices</t>
+          <t>travel_class_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'business'}</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Business'}</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>travel_class_choices</t>
+          <t>travel_class_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'personal'}</t>
+          <t>personal</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Personal'}</t>
+          <t>Personal</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>travel_class_choices</t>
+          <t>travel_class_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'company'}</t>
+          <t>company</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Company'}</t>
+          <t>Company</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>submitted_user_choices</t>
+          <t>submitted_user_3_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'chatjimmy',_'value':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'chatjimmy', 'value': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>submitted_user_choices</t>
+          <t>submitted_user_3_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
